--- a/보장진단_김선우.xlsx
+++ b/보장진단_김선우.xlsx
@@ -3585,7 +3585,7 @@
       <c r="I77" s="174" t="n"/>
       <c r="J77" s="174" t="n"/>
       <c r="K77" s="175">
-        <f>SUM(C77:J77)</f>
+        <f>IF(COUNT(C77:J77)=0,0,MAX(C77:J77))</f>
         <v>0</v>
       </c>
     </row>
@@ -4308,7 +4308,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>김선우 · 자동분석 2026.07.02</t>
+          <t>김선우 · 자동분석 2026.07.03</t>
         </is>
       </c>
     </row>
